--- a/Luban/Config/Datas/#MapConfig.xlsx
+++ b/Luban/Config/Datas/#MapConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2B5307-2903-4E53-B22F-785E420C4543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ED124E-18F1-4BDA-B272-DEF5E556563C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5250" yWindow="3825" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
